--- a/public/Plantilla_Registro_Clientes_SERGEM.xlsx
+++ b/public/Plantilla_Registro_Clientes_SERGEM.xlsx
@@ -3,8 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Clientes_SERGEM" sheetId="1" r:id="rId1"/>
-    <sheet name="Guia_y_Condiciones" sheetId="2" r:id="rId2"/>
+    <sheet name="Jerarquia_Clientes_SERGEM" sheetId="1" r:id="rId1"/>
+    <sheet name="Guia_Jerarquia_SERGEM" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -398,49 +398,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J4"/>
-  <cols>
-    <col min="1" max="1" width="22.83203125" customWidth="1"/>
-    <col min="2" max="2" width="38.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="38.83203125" customWidth="1"/>
-    <col min="5" max="5" width="28.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="32.83203125" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" customWidth="1"/>
-    <col min="9" max="9" width="45.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:N5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>NIT / Identificación</v>
+        <v>NIT Empresa *</v>
       </c>
       <c r="B1" t="str">
-        <v>Nombre o Razón Social *</v>
+        <v>Razón Social / Empresa *</v>
       </c>
       <c r="C1" t="str">
+        <v>Código Centro Costo *</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Nombre Centro Costo *</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Código Punto Venta</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Nombre Punto de Venta / Sede *</v>
+      </c>
+      <c r="G1" t="str">
         <v>Ciudad *</v>
       </c>
-      <c r="D1" t="str">
+      <c r="H1" t="str">
         <v>Dirección de Sede / Muelle</v>
       </c>
-      <c r="E1" t="str">
+      <c r="I1" t="str">
         <v>Nombre Supervisor / Contacto</v>
       </c>
-      <c r="F1" t="str">
+      <c r="J1" t="str">
         <v>Teléfono Celular (WhatsApp)</v>
       </c>
-      <c r="G1" t="str">
+      <c r="K1" t="str">
         <v>Correo Electrónico Contacto</v>
       </c>
-      <c r="H1" t="str">
+      <c r="L1" t="str">
         <v>Tarifa Base por Hora ($ COP)</v>
       </c>
-      <c r="I1" t="str">
+      <c r="M1" t="str">
         <v>Observaciones Operativas / EPP</v>
       </c>
-      <c r="J1" t="str">
+      <c r="N1" t="str">
         <v>Estado (Activo / Inactivo)</v>
       </c>
     </row>
@@ -449,122 +449,196 @@
         <v>890.900.608-9</v>
       </c>
       <c r="B2" t="str">
-        <v>ALKOSTO CALI (HIPERAHORRO)</v>
+        <v>ALKOSTO CALI S.A.</v>
       </c>
       <c r="C2" t="str">
+        <v>CC-VALLE-01</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Operación Logística Valle del Cauca</v>
+      </c>
+      <c r="E2" t="str">
+        <v>PV-PASOANCHO</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Alkosto Pasoancho (Hiperahorro)</v>
+      </c>
+      <c r="G2" t="str">
         <v>Cali</v>
       </c>
-      <c r="D2" t="str">
+      <c r="H2" t="str">
         <v>Av. Pasoancho # 80-120, Bodega 4</v>
       </c>
-      <c r="E2" t="str">
+      <c r="I2" t="str">
         <v>Liceth Morales</v>
       </c>
-      <c r="F2" t="str">
+      <c r="J2" t="str">
         <v>3154567890</v>
       </c>
-      <c r="G2" t="str">
+      <c r="K2" t="str">
         <v>logistica.cali@alkosto.com.co</v>
       </c>
-      <c r="H2">
+      <c r="L2">
         <v>12500</v>
       </c>
-      <c r="I2" t="str">
+      <c r="M2" t="str">
         <v>Ingreso con botas de seguridad y carné de ARL vigente. Despacho matutino.</v>
       </c>
-      <c r="J2" t="str">
+      <c r="N2" t="str">
         <v>Activo</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>900.123.456-1</v>
+        <v>890.900.608-1</v>
       </c>
       <c r="B3" t="str">
-        <v>TCC LOGÍSTICA S.A.S. - VALLE</v>
+        <v>ALMACENES ÉXITO S.A.</v>
       </c>
       <c r="C3" t="str">
-        <v>Yumbo</v>
+        <v>CC-EXITO-CALI</v>
       </c>
       <c r="D3" t="str">
-        <v>Zona Industrial Acopi, Calle 15 # 22-45</v>
+        <v>Reparto Express y Última Milla</v>
       </c>
       <c r="E3" t="str">
-        <v>Ing. Carlos Ruiz</v>
+        <v>PV-CHIPICHAPE</v>
       </c>
       <c r="F3" t="str">
-        <v>3109876543</v>
+        <v>Éxito Chipichape Sede Norte</v>
       </c>
       <c r="G3" t="str">
-        <v>operaciones.valle@tcc.com.co</v>
-      </c>
-      <c r="H3">
-        <v>14000</v>
+        <v>Cali</v>
+      </c>
+      <c r="H3" t="str">
+        <v>Calle 38 Norte # 6N-35</v>
       </c>
       <c r="I3" t="str">
-        <v>Cargue diario de 6:00 AM a 8:00 AM. Control estricto de paquetes y remisiones.</v>
+        <v>Carlos Méndez</v>
       </c>
       <c r="J3" t="str">
+        <v>3168889911</v>
+      </c>
+      <c r="K3" t="str">
+        <v>despachos.chipichape@exito.com</v>
+      </c>
+      <c r="L3">
+        <v>13000</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Control de precintos y entrega con datáfono.</v>
+      </c>
+      <c r="N3" t="str">
         <v>Activo</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>900.123.456-1</v>
+      </c>
+      <c r="B4" t="str">
+        <v>TCC LOGÍSTICA S.A.S.</v>
+      </c>
+      <c r="C4" t="str">
+        <v>CC-TCC-IND</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Zona Industrial Acopi y Envíos Masivos</v>
+      </c>
+      <c r="E4" t="str">
+        <v>PV-ACOPI-01</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Muelle Principal Acopi Yumbo</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Yumbo</v>
+      </c>
+      <c r="H4" t="str">
+        <v>Zona Industrial Acopi, Calle 15 # 22-45</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Ing. Carlos Ruiz</v>
+      </c>
+      <c r="J4" t="str">
+        <v>3109876543</v>
+      </c>
+      <c r="K4" t="str">
+        <v>operaciones.valle@tcc.com.co</v>
+      </c>
+      <c r="L4">
+        <v>14000</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Cargue diario de 6:00 AM a 8:00 AM. Control estricto de paquetes y remisiones.</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Activo</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
         <v>901.456.789-2</v>
       </c>
-      <c r="B4" t="str">
+      <c r="B5" t="str">
         <v>DISTRIBUIDORA DE MEDICAMENTOS DEL VALLE S.A.S.</v>
       </c>
-      <c r="C4" t="str">
+      <c r="C5" t="str">
+        <v>CC-FARMA-VALLE</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Cadena de Frío y Farmacéutica</v>
+      </c>
+      <c r="E5" t="str">
+        <v>PV-DOLORES-12</v>
+      </c>
+      <c r="F5" t="str">
+        <v>Sede Parque Industrial La Dolores</v>
+      </c>
+      <c r="G5" t="str">
         <v>Palmira</v>
       </c>
-      <c r="D4" t="str">
+      <c r="H5" t="str">
         <v>Parque Industrial La Dolores, Bodega 12</v>
       </c>
-      <c r="E4" t="str">
+      <c r="I5" t="str">
         <v>Dra. Patricia Gómez</v>
       </c>
-      <c r="F4" t="str">
+      <c r="J5" t="str">
         <v>3201234567</v>
       </c>
-      <c r="G4" t="str">
+      <c r="K5" t="str">
         <v>despachos@distrimedvalle.com</v>
       </c>
-      <c r="H4">
+      <c r="L5">
         <v>13500</v>
       </c>
-      <c r="I4" t="str">
+      <c r="M5" t="str">
         <v>Exclusivo reparto motorizado con maletín térmico para transporte de medicamentos.</v>
       </c>
-      <c r="J4" t="str">
+      <c r="N5" t="str">
         <v>Activo</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D16"/>
-  <cols>
-    <col min="1" max="1" width="25.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="60.83203125" customWidth="1"/>
-    <col min="4" max="4" width="28.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:E18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>SERGEM MENSAJERÍA Y LOGÍSTICA S.A.S. - GUÍA DE CARGA MASIVA DE CLIENTES</v>
+        <v>SERGEM MENSAJERÍA Y LOGÍSTICA S.A.S. - GUÍA DE ESTRUCTURA Y CARGA JERÁRQUICA</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Instrucciones para diligenciar la plantilla oficial de clientes corporativos:</v>
+        <v>Estructura organizacional oficial: 1. Empresa -&gt; 2. Centro de Costo -&gt; 3. Punto de Venta (con Ciudad)</v>
       </c>
     </row>
     <row r="3">
@@ -574,171 +648,262 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Campo</v>
+        <v>Nivel Jerárquico</v>
       </c>
       <c r="B4" t="str">
+        <v>Campo en Plantilla</v>
+      </c>
+      <c r="C4" t="str">
         <v>Obligatorio</v>
       </c>
-      <c r="C4" t="str">
-        <v>Descripción y Formato</v>
-      </c>
       <c r="D4" t="str">
+        <v>Descripción</v>
+      </c>
+      <c r="E4" t="str">
         <v>Ejemplo</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>NIT / Identificación</v>
+        <v>Nivel 1: EMPRESA</v>
       </c>
       <c r="B5" t="str">
-        <v>Opcional</v>
+        <v>NIT Empresa</v>
       </c>
       <c r="C5" t="str">
-        <v>Número de Identificación Tributaria con o sin guion</v>
+        <v>Recomendado</v>
       </c>
       <c r="D5" t="str">
+        <v>NIT tributario de la empresa cliente con o sin dígito de verificación</v>
+      </c>
+      <c r="E5" t="str">
         <v>890.900.608-9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Nombre o Razón Social</v>
+        <v>Nivel 1: EMPRESA</v>
       </c>
       <c r="B6" t="str">
+        <v>Razón Social / Empresa</v>
+      </c>
+      <c r="C6" t="str">
         <v>SÍ (Obligatorio)</v>
       </c>
-      <c r="C6" t="str">
-        <v>Razón social completa o nombre comercial de la empresa cliente</v>
-      </c>
       <c r="D6" t="str">
-        <v>ALKOSTO CALI</v>
+        <v>Nombre legal o corporativo de la empresa</v>
+      </c>
+      <c r="E6" t="str">
+        <v>ALKOSTO CALI S.A.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Ciudad</v>
+        <v>Nivel 2: CENTRO DE COSTO</v>
       </c>
       <c r="B7" t="str">
-        <v>Recomendado</v>
+        <v>Código Centro Costo</v>
       </c>
       <c r="C7" t="str">
-        <v>Ciudad sede de despacho (Cali, Yumbo, Palmira, Jamundí, etc.)</v>
+        <v>SÍ (Obligatorio)</v>
       </c>
       <c r="D7" t="str">
-        <v>Cali</v>
+        <v>Código interno para imputación presupuestal y operativa</v>
+      </c>
+      <c r="E7" t="str">
+        <v>CC-VALLE-01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Dirección de Sede</v>
+        <v>Nivel 2: CENTRO DE COSTO</v>
       </c>
       <c r="B8" t="str">
-        <v>Opcional</v>
+        <v>Nombre Centro Costo</v>
       </c>
       <c r="C8" t="str">
-        <v>Dirección de bodega, muelle o sede administrativa</v>
+        <v>SÍ (Obligatorio)</v>
       </c>
       <c r="D8" t="str">
-        <v>Av. Pasoancho # 80-120</v>
+        <v>Denominación de la línea, contrato o centro de costo</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Operación Logística Valle</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Nombre Supervisor</v>
+        <v>Nivel 3: PUNTO DE VENTA</v>
       </c>
       <c r="B9" t="str">
+        <v>Código Punto Venta</v>
+      </c>
+      <c r="C9" t="str">
         <v>Opcional</v>
       </c>
-      <c r="C9" t="str">
-        <v>Persona encargada de coordinar los repartidores de SERGEM</v>
-      </c>
       <c r="D9" t="str">
-        <v>Liceth Morales</v>
+        <v>Código o identificador de tienda, sucursal o muelle</v>
+      </c>
+      <c r="E9" t="str">
+        <v>PV-PASOANCHO</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Teléfono Celular</v>
+        <v>Nivel 3: PUNTO DE VENTA</v>
       </c>
       <c r="B10" t="str">
-        <v>Opcional</v>
+        <v>Nombre Punto de Venta / Sede</v>
       </c>
       <c r="C10" t="str">
-        <v>Número móvil o fijo para contacto y notificaciones WhatsApp</v>
+        <v>SÍ (Obligatorio)</v>
       </c>
       <c r="D10" t="str">
-        <v>3154567890</v>
+        <v>Sede física donde opera el repartidor o mensajero</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Alkosto Pasoancho (Hiperahorro)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Correo Electrónico</v>
+        <v>Nivel 3: PUNTO DE VENTA</v>
       </c>
       <c r="B11" t="str">
-        <v>Opcional</v>
+        <v>Ciudad</v>
       </c>
       <c r="C11" t="str">
-        <v>Correo para envío de informes y novedades operativas</v>
+        <v>SÍ (Obligatorio)</v>
       </c>
       <c r="D11" t="str">
-        <v>logistica@cliente.com</v>
+        <v>Ciudad de la sede (Cali, Yumbo, Palmira, Jamundí, Bogotá, Medellín, etc.)</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Cali</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Tarifa Base por Hora</v>
+        <v>Nivel 3: PUNTO DE VENTA</v>
       </c>
       <c r="B12" t="str">
+        <v>Dirección de Sede / Muelle</v>
+      </c>
+      <c r="C12" t="str">
         <v>Opcional</v>
       </c>
-      <c r="C12" t="str">
-        <v>Tarifa estándar acordada por hora de servicio (número sin puntos)</v>
-      </c>
       <c r="D12" t="str">
-        <v>12500</v>
+        <v>Dirección física completa del muelle o punto de despacho</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Av. Pasoancho # 80-120</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Observaciones</v>
+        <v>Nivel 3: PUNTO DE VENTA</v>
       </c>
       <c r="B13" t="str">
+        <v>Nombre Supervisor</v>
+      </c>
+      <c r="C13" t="str">
         <v>Opcional</v>
       </c>
-      <c r="C13" t="str">
-        <v>Requisitos de EPP, horarios de descargue o restricciones</v>
-      </c>
       <c r="D13" t="str">
-        <v>Uso obligatorio de chaleco</v>
+        <v>Supervisor de tienda o contacto encargado</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Liceth Morales</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Estado</v>
+        <v>Nivel 3: PUNTO DE VENTA</v>
       </c>
       <c r="B14" t="str">
+        <v>Teléfono Celular (WhatsApp)</v>
+      </c>
+      <c r="C14" t="str">
         <v>Opcional</v>
       </c>
-      <c r="C14" t="str">
-        <v>Activo o Inactivo (por defecto Activo)</v>
-      </c>
       <c r="D14" t="str">
-        <v>Activo</v>
+        <v>Número móvil para enlace directo y llamadas</v>
+      </c>
+      <c r="E14" t="str">
+        <v>3154567890</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v/>
+        <v>Nivel 3: PUNTO DE VENTA</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Correo Electrónico</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Opcional</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Correo para remisiones e informes</v>
+      </c>
+      <c r="E15" t="str">
+        <v>logistica@alkosto.com.co</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Nota importante: Puedes dejar o eliminar las 3 filas de ejemplo. La plataforma detectará automáticamente si son de prueba y te permitirá desmarcarlas con un solo clic.</v>
+        <v>Nivel 3: PUNTO DE VENTA</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Tarifa Base por Hora</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Opcional</v>
+      </c>
+      <c r="D16" t="str">
+        <v>Tarifa acordada por hora de servicio (número sin puntos)</v>
+      </c>
+      <c r="E16" t="str">
+        <v>12500</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>Nivel 3: PUNTO DE VENTA</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Observaciones / EPP</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Opcional</v>
+      </c>
+      <c r="D17" t="str">
+        <v>Requisitos de EPP, horarios de descargue o restricciones</v>
+      </c>
+      <c r="E17" t="str">
+        <v>Uso obligatorio de botas y chaleco</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>Nivel 3: PUNTO DE VENTA</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Estado</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Opcional</v>
+      </c>
+      <c r="D18" t="str">
+        <v>Activo o Inactivo</v>
+      </c>
+      <c r="E18" t="str">
+        <v>Activo</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E18"/>
   </ignoredErrors>
 </worksheet>
 </file>